--- a/output/pdf_financials_xlsx/AXL.xlsx
+++ b/output/pdf_financials_xlsx/AXL.xlsx
@@ -1316,13 +1316,13 @@
         <v>-0.362307</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.06949</v>
+        <v>-0.06949</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>-3.922836</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>8.374923000000001</v>
+        <v>-5.780517</v>
       </c>
       <c r="J16" s="3" t="n">
         <v>-0.004228</v>
@@ -1608,13 +1608,13 @@
         <v>-0.362307</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.06949</v>
+        <v>-0.06949</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>-3.922836</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>7.07772</v>
+        <v>-7.07772</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>-0.004228</v>
@@ -1781,13 +1781,13 @@
         <v>-0.362307</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.06949</v>
+        <v>-0.06949</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>-3.922836</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>7.07772</v>
+        <v>-7.07772</v>
       </c>
       <c r="J23" s="3" t="n">
         <v>-0.004228</v>
@@ -1972,7 +1972,7 @@
         <v>7.132429</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>25.277571</v>
+        <v>-25.277571</v>
       </c>
       <c r="J26" s="1" t="inlineStr">
         <is>
@@ -2029,13 +2029,13 @@
         <v>-0.362307</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.06949</v>
+        <v>-0.06949</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>-3.922836</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>8.374923000000001</v>
+        <v>-5.780517</v>
       </c>
       <c r="J27" s="3" t="n">
         <v>-0.004228</v>
@@ -2147,13 +2147,13 @@
         <v>0.179547</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.628667</v>
+        <v>0.489687</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>-3.453008</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>9.303236999999999</v>
+        <v>-4.852203</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0.27407</v>
@@ -2206,13 +2206,13 @@
         <v>8.733276748082952</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>30.00726951971052</v>
+        <v>23.37353446148515</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>-272.0139780041798</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>787.4469610467877</v>
+        <v>-410.7014049767953</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>31.5195077772347</v>
@@ -2275,13 +2275,13 @@
         <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>15.48913345233144</v>
+        <v>-22.44095121595525</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>-60087.86660359508</v>
@@ -2334,13 +2334,13 @@
         <v>-17.62283579657521</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>3.316867529112684</v>
+        <v>-3.316867529112684</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>-309.0251240130358</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>599.0741830117914</v>
+        <v>-599.0741830117914</v>
       </c>
       <c r="J32" s="3" t="n">
         <v>-0.486242488715103</v>
@@ -5659,25 +5659,25 @@
         <v>3.437756</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>2.581003</v>
+        <v>0.127052</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.705109</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.232733</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.808176</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.78313</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.971879</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>0.800787</v>
@@ -17370,7 +17370,11 @@
           <t>Share-based payment reserve 12</t>
         </is>
       </c>
-      <c r="D97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E97" t="inlineStr">
         <is>
           <t>-</t>
@@ -18396,7 +18400,11 @@
           <t>Share-based payment reserve</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr"/>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E108" t="inlineStr">
         <is>
           <t>-</t>
@@ -19054,7 +19062,11 @@
           <t>Share-based payment reserve 11</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
           <t>-</t>
@@ -21182,7 +21194,11 @@
           <t>Share-based payment reserve 2,129,738</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E137" t="inlineStr">
         <is>
           <t>-</t>
@@ -56513,10 +56529,10 @@
         <v>-3.922836</v>
       </c>
       <c r="L508" s="5" t="n">
-        <v>7.07772</v>
+        <v>-7.07772</v>
       </c>
       <c r="M508" s="5" t="n">
-        <v>28.401589</v>
+        <v>-28.401589</v>
       </c>
       <c r="N508" t="inlineStr">
         <is>
@@ -58595,10 +58611,10 @@
         </is>
       </c>
       <c r="J530" s="5" t="n">
-        <v>0.06949</v>
+        <v>-0.06949</v>
       </c>
       <c r="K530" s="5" t="n">
-        <v>3.922836</v>
+        <v>-3.922836</v>
       </c>
       <c r="L530" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/AXL.xlsx
+++ b/output/pdf_financials_xlsx/AXL.xlsx
@@ -1077,19 +1077,19 @@
         <v>0.138762</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.02088</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.028093</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.040266</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09192699999999999</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.100485</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>0</v>
@@ -2026,19 +2026,19 @@
         <v>-0.555203</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.362307</v>
+        <v>-0.341427</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.06949</v>
+        <v>-0.041397</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-3.922836</v>
+        <v>-3.88257</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-5.780517</v>
+        <v>-5.68859</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.004228</v>
+        <v>0.096257</v>
       </c>
       <c r="K27" s="3" t="n">
         <v>-0.590123</v>
@@ -2144,19 +2144,19 @@
         <v>-0.191399</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.179547</v>
+        <v>0.200427</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.489687</v>
+        <v>0.51778</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-3.453008</v>
+        <v>-3.412742</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-4.852203</v>
+        <v>-4.760276</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.27407</v>
+        <v>0.374555</v>
       </c>
       <c r="K29" s="3" t="n">
         <v>1.453997</v>
@@ -2203,19 +2203,19 @@
         <v>-13.23834963812222</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>8.733276748082952</v>
+        <v>9.748892817969789</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>23.37353446148515</v>
+        <v>24.71445775253944</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>-272.0139780041798</v>
+        <v>-268.8419856895613</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>-410.7014049767953</v>
+        <v>-402.9204963760418</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>31.5195077772347</v>
+        <v>43.07581725654811</v>
       </c>
       <c r="K30" s="3" t="n">
         <v>23.92456473738951</v>
@@ -2391,22 +2391,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.505377</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.6484</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.6484</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>8.343367000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>3.551115</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>7.200072</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>3.76135</v>
@@ -2415,28 +2415,28 @@
         <v>26.186723</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>3.044268</v>
+        <v>0.007966000000000001</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.994233</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>1.085655</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>10.878508</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>13.060968</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>12.135376</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>18.837784</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>11.208824</v>
       </c>
     </row>
     <row r="35">
@@ -2501,22 +2501,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.505377</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.6484</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.6484</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>8.343367000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>3.551115</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>7.200072</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>3.76135</v>
@@ -2525,28 +2525,28 @@
         <v>26.186723</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>3.044268</v>
+        <v>0.007966000000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>1.994233</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>1.085655</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>10.878508</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>13.060968</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>12.135376</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>18.837784</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>11.208824</v>
       </c>
     </row>
     <row r="37">
@@ -3161,22 +3161,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.508544</v>
+        <v>0.003167</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.660463</v>
+        <v>0.012063</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.660463</v>
+        <v>0.012063</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>8.421528</v>
+        <v>0.07816099999999999</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>3.612396</v>
+        <v>0.061281</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>7.272541</v>
+        <v>0.07246900000000001</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.172957</v>
@@ -3185,28 +3185,28 @@
         <v>0.08781700000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.5380740000000001</v>
+        <v>3.574376</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.160167</v>
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>3.706395</v>
+        <v>2.62074</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>11.919857</v>
+        <v>1.041349</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>14.230258</v>
+        <v>1.16929</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>17.59993</v>
+        <v>5.464554</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>21.965581</v>
+        <v>3.127797</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>19.239393</v>
+        <v>8.030569</v>
       </c>
     </row>
     <row r="49">
@@ -7609,22 +7609,22 @@
         <v>0</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.071468</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.024535</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>-0.023076</v>
+        <v>-0.062773</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.074211</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.057807</v>
       </c>
       <c r="Q124" s="3" t="n">
-        <v>0</v>
+        <v>-0.076048</v>
       </c>
     </row>
     <row r="125">
@@ -7672,22 +7672,22 @@
         <v>0</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.071468</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.024535</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>-0.023076</v>
+        <v>-0.062773</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.074211</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.057807</v>
       </c>
       <c r="Q125" s="3" t="n">
-        <v>0</v>
+        <v>-0.076048</v>
       </c>
     </row>
     <row r="126">
@@ -8582,7 +8582,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -19650,7 +19650,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -25732,7 +25732,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D185" t="inlineStr"/>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
           <t>-</t>
@@ -27066,7 +27070,11 @@
           <t>Lease payments 9</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -28770,7 +28778,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D217" t="inlineStr"/>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E217" t="inlineStr">
         <is>
           <t>-</t>
@@ -32340,7 +32352,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
@@ -55272,7 +55288,7 @@
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
